--- a/data/raw/All Treatments/combined_raw.xlsx
+++ b/data/raw/All Treatments/combined_raw.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ey239/Github/Mowtivation/data/raw/All Treatments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB96A0D8-4C6C-9C49-8DFF-B4492D6F283B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1757DF03-7787-8C40-BEE2-545578492D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10440" yWindow="-27520" windowWidth="34160" windowHeight="20040" xr2:uid="{BC6E1F37-F489-F945-938B-9CB0E83CEE7D}"/>
+    <workbookView xWindow="3680" yWindow="-20800" windowWidth="19220" windowHeight="21000" xr2:uid="{BC6E1F37-F489-F945-938B-9CB0E83CEE7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$N$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="89">
   <si>
     <t>id</t>
   </si>
@@ -77,101 +77,242 @@
     <t>bean_yield</t>
   </si>
   <si>
-    <t>CU_B1_P101</t>
-  </si>
-  <si>
     <t>TIM</t>
   </si>
   <si>
-    <t>CU_B1_P102</t>
-  </si>
-  <si>
     <t>TIC</t>
   </si>
   <si>
-    <t>CU_B1_P103</t>
-  </si>
-  <si>
     <t>RIM</t>
   </si>
   <si>
-    <t>CU_B1_P104</t>
-  </si>
-  <si>
     <t>RNO</t>
   </si>
   <si>
-    <t>CU_B1_P105</t>
-  </si>
-  <si>
     <t>RIC</t>
   </si>
   <si>
-    <t>CU_B1_P201</t>
-  </si>
-  <si>
-    <t>CU_B1_P202</t>
-  </si>
-  <si>
-    <t>CU_B1_P203</t>
-  </si>
-  <si>
-    <t>CU_B1_P204</t>
-  </si>
-  <si>
-    <t>CU_B1_P205</t>
-  </si>
-  <si>
-    <t>CU_B1_P301</t>
-  </si>
-  <si>
-    <t>CU_B1_P302</t>
-  </si>
-  <si>
-    <t>CU_B1_P303</t>
-  </si>
-  <si>
-    <t>CU_B1_P304</t>
-  </si>
-  <si>
-    <t>CU_B1_P305</t>
-  </si>
-  <si>
-    <t>CU_B1_P401</t>
-  </si>
-  <si>
-    <t>CU_B1_P402</t>
-  </si>
-  <si>
-    <t>CU_B1_P403</t>
-  </si>
-  <si>
-    <t>CU_B1_P404</t>
-  </si>
-  <si>
-    <t>CU_B1_P405</t>
-  </si>
-  <si>
-    <t>field O2 west</t>
-  </si>
-  <si>
-    <t>field O2 east</t>
-  </si>
-  <si>
     <t>seed_weight</t>
   </si>
   <si>
-    <t>field v</t>
-  </si>
-  <si>
     <t>inrow_weed_biomass</t>
+  </si>
+  <si>
+    <t>V</t>
+  </si>
+  <si>
+    <t>O2W</t>
+  </si>
+  <si>
+    <t>O2E</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P101</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P102</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P103</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P104</t>
+  </si>
+  <si>
+    <t>V_2023_B1_P105</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P201</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P202</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P203</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P204</t>
+  </si>
+  <si>
+    <t>V_2023_B2_P205</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P301</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P302</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P303</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P304</t>
+  </si>
+  <si>
+    <t>V_2023_B3_P305</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P401</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P402</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P403</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P404</t>
+  </si>
+  <si>
+    <t>V_2023_B4_P405</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P101</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P102</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P103</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P104</t>
+  </si>
+  <si>
+    <t>O2W_2024_B1_P105</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P201</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P202</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P203</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P204</t>
+  </si>
+  <si>
+    <t>O2W_2024_B2_P205</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P301</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P302</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P303</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P304</t>
+  </si>
+  <si>
+    <t>O2W_2024_B3_P305</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P401</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P402</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P403</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P404</t>
+  </si>
+  <si>
+    <t>O2W_2024_B4_P405</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P101</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P102</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P103</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P104</t>
+  </si>
+  <si>
+    <t>O2E_2024_B1_P105</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P201</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P202</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P203</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P204</t>
+  </si>
+  <si>
+    <t>O2E_2024_B2_P205</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P301</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P302</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P303</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P304</t>
+  </si>
+  <si>
+    <t>O2E_2024_B3_P305</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P401</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P402</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P403</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P404</t>
+  </si>
+  <si>
+    <t>O2E_2024_B4_P405</t>
+  </si>
+  <si>
+    <t>interrow_mulch_biomass</t>
+  </si>
+  <si>
+    <t>mulch_biomass</t>
+  </si>
+  <si>
+    <t>inrow_mulch_biomass</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>cereal_rye_variety</t>
+  </si>
+  <si>
+    <t>aroostook</t>
+  </si>
+  <si>
+    <t>nd gardner</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -182,6 +323,12 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -242,7 +389,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -250,9 +396,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,22 +739,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8CD3FB9F-C7C0-8845-8916-2E1AAB9BD4F0}">
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:R61"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="20.83203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" customWidth="1"/>
+    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="17" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -617,2677 +773,3411 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="Q1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="N1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C2" s="6">
         <v>2023</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="6">
+        <v>12</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" s="6">
         <v>1</v>
       </c>
-      <c r="F2" s="6">
+      <c r="G2" s="6">
         <v>101</v>
       </c>
-      <c r="G2">
+      <c r="H2" s="5">
         <v>46.5</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="5">
         <v>223.74</v>
       </c>
-      <c r="I2">
+      <c r="J2" s="5">
         <v>19</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="5">
         <v>44.489999999999995</v>
       </c>
-      <c r="K2">
+      <c r="L2" s="5">
         <v>63.489999999999995</v>
       </c>
-      <c r="L2">
+      <c r="M2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O2" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="5">
         <v>34.5</v>
       </c>
-      <c r="M2" s="6">
+      <c r="Q2" s="6">
         <v>417.21</v>
       </c>
-      <c r="N2">
+      <c r="R2" s="5">
         <v>17.119999999999997</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C3" s="6">
         <v>2023</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="6">
+        <v>13</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F3" s="6">
         <v>1</v>
       </c>
-      <c r="F3" s="6">
+      <c r="G3" s="6">
         <v>102</v>
       </c>
-      <c r="G3">
+      <c r="H3" s="5">
         <v>42.5</v>
       </c>
-      <c r="H3">
+      <c r="I3" s="5">
         <v>267.45999999999998</v>
       </c>
-      <c r="I3">
+      <c r="J3" s="5">
         <v>30.975000000000001</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="5">
         <v>0.72</v>
       </c>
-      <c r="K3">
+      <c r="L3" s="5">
         <v>31.695</v>
       </c>
-      <c r="L3">
+      <c r="M3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P3" s="5">
         <v>39.5</v>
       </c>
-      <c r="M3" s="6">
+      <c r="Q3" s="6">
         <v>565.54</v>
       </c>
-      <c r="N3">
+      <c r="R3" s="5">
         <v>17.475000000000001</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C4" s="6">
         <v>2023</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="6">
+        <v>14</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="6">
         <v>1</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <v>103</v>
       </c>
-      <c r="G4">
+      <c r="H4" s="5">
         <v>36.5</v>
       </c>
-      <c r="H4">
+      <c r="I4" s="5">
         <v>217.89</v>
       </c>
-      <c r="I4">
+      <c r="J4" s="5">
         <v>0.95</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="5">
         <v>6.89</v>
       </c>
-      <c r="K4">
+      <c r="L4" s="5">
         <v>7.84</v>
       </c>
-      <c r="L4">
+      <c r="M4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O4">
+        <v>285.95</v>
+      </c>
+      <c r="P4" s="5">
         <v>37.5</v>
       </c>
-      <c r="M4" s="6">
+      <c r="Q4" s="6">
         <v>449.93</v>
       </c>
-      <c r="N4">
+      <c r="R4" s="5">
         <v>16.752499999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C5" s="6">
         <v>2023</v>
       </c>
       <c r="D5" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F5" s="6">
+        <v>1</v>
+      </c>
+      <c r="G5" s="6">
+        <v>104</v>
+      </c>
+      <c r="H5" s="5">
+        <v>41</v>
+      </c>
+      <c r="I5" s="5">
+        <v>207.67500000000001</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0.65999999999999992</v>
+      </c>
+      <c r="K5" s="5">
+        <v>45.734999999999999</v>
+      </c>
+      <c r="L5" s="5">
+        <v>46.394999999999996</v>
+      </c>
+      <c r="M5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N5" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O5">
+        <v>241.03000000000003</v>
+      </c>
+      <c r="P5" s="5">
+        <v>35</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>412.59</v>
+      </c>
+      <c r="R5" s="5">
+        <v>16.145</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="E5" s="6">
-        <v>1</v>
-      </c>
-      <c r="F5" s="6">
-        <v>104</v>
-      </c>
-      <c r="G5">
-        <v>41</v>
-      </c>
-      <c r="H5">
-        <v>207.67500000000001</v>
-      </c>
-      <c r="I5">
-        <v>0.65999999999999992</v>
-      </c>
-      <c r="J5">
-        <v>45.734999999999999</v>
-      </c>
-      <c r="K5">
-        <v>46.394999999999996</v>
-      </c>
-      <c r="L5">
-        <v>35</v>
-      </c>
-      <c r="M5" s="6">
-        <v>412.59</v>
-      </c>
-      <c r="N5">
-        <v>16.145</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C6" s="6">
         <v>2023</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" s="6">
+        <v>16</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="6">
         <v>1</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <v>105</v>
       </c>
-      <c r="G6">
+      <c r="H6" s="5">
         <v>41</v>
       </c>
-      <c r="H6">
+      <c r="I6" s="5">
         <v>230.28500000000003</v>
       </c>
-      <c r="I6">
+      <c r="J6" s="5">
         <v>0.495</v>
       </c>
-      <c r="J6">
+      <c r="K6" s="5">
         <v>22.024999999999999</v>
       </c>
-      <c r="K6">
+      <c r="L6" s="5">
         <v>22.52</v>
       </c>
-      <c r="L6">
+      <c r="M6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O6">
+        <v>306.64</v>
+      </c>
+      <c r="P6" s="5">
         <v>39</v>
       </c>
-      <c r="M6" s="6">
+      <c r="Q6" s="6">
         <v>473.79</v>
       </c>
-      <c r="N6">
+      <c r="R6" s="5">
         <v>17.047499999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C7" s="6">
         <v>2023</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="6">
+        <v>16</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="6">
         <v>2</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <v>201</v>
       </c>
-      <c r="G7">
+      <c r="H7" s="5">
         <v>36.5</v>
       </c>
-      <c r="H7">
+      <c r="I7" s="5">
         <v>208.10500000000002</v>
       </c>
-      <c r="I7">
+      <c r="J7" s="5">
         <v>6.3950000000000005</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="5">
         <v>19.46</v>
       </c>
-      <c r="K7">
+      <c r="L7" s="5">
         <v>25.855</v>
       </c>
-      <c r="L7">
+      <c r="M7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N7" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O7">
+        <v>370.94499999999999</v>
+      </c>
+      <c r="P7" s="5">
         <v>33.5</v>
       </c>
-      <c r="M7" s="6">
+      <c r="Q7" s="6">
         <v>484.04</v>
       </c>
-      <c r="N7">
+      <c r="R7" s="5">
         <v>17.149999999999999</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6">
         <v>2023</v>
       </c>
       <c r="D8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F8" s="6">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>202</v>
+      </c>
+      <c r="H8" s="5">
+        <v>39</v>
+      </c>
+      <c r="I8" s="5">
+        <v>232.80500000000001</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1.4350000000000001</v>
+      </c>
+      <c r="K8" s="5">
+        <v>22.19</v>
+      </c>
+      <c r="L8" s="5">
+        <v>23.625</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O8">
+        <v>344.27499999999998</v>
+      </c>
+      <c r="P8" s="5">
+        <v>34</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>556.76</v>
+      </c>
+      <c r="R8" s="5">
+        <v>16.392500000000002</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2</v>
-      </c>
-      <c r="F8" s="6">
-        <v>202</v>
-      </c>
-      <c r="G8">
-        <v>39</v>
-      </c>
-      <c r="H8">
-        <v>232.80500000000001</v>
-      </c>
-      <c r="I8">
-        <v>1.4350000000000001</v>
-      </c>
-      <c r="J8">
-        <v>22.19</v>
-      </c>
-      <c r="K8">
-        <v>23.625</v>
-      </c>
-      <c r="L8">
-        <v>34</v>
-      </c>
-      <c r="M8" s="6">
-        <v>556.76</v>
-      </c>
-      <c r="N8">
-        <v>16.392500000000002</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C9" s="6">
         <v>2023</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E9" s="6">
+        <v>14</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F9" s="6">
         <v>2</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <v>203</v>
       </c>
-      <c r="G9">
+      <c r="H9" s="5">
         <v>40</v>
       </c>
-      <c r="H9">
+      <c r="I9" s="5">
         <v>228.69499999999999</v>
       </c>
-      <c r="I9">
+      <c r="J9" s="5">
         <v>13.18</v>
       </c>
-      <c r="J9">
+      <c r="K9" s="5">
         <v>7.625</v>
       </c>
-      <c r="K9">
+      <c r="L9" s="5">
         <v>20.805</v>
       </c>
-      <c r="L9">
+      <c r="M9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O9">
+        <v>210.61</v>
+      </c>
+      <c r="P9" s="5">
         <v>32</v>
       </c>
-      <c r="M9" s="6">
+      <c r="Q9" s="6">
         <v>497.82</v>
       </c>
-      <c r="N9">
+      <c r="R9" s="5">
         <v>16.517500000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="6" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C10" s="6">
         <v>2023</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" s="6">
+        <v>13</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F10" s="6">
         <v>2</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <v>204</v>
       </c>
-      <c r="G10">
+      <c r="H10" s="5">
         <v>45.5</v>
       </c>
-      <c r="H10">
+      <c r="I10" s="5">
         <v>268.27</v>
       </c>
-      <c r="I10">
+      <c r="J10" s="5">
         <v>65.424999999999997</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="5">
         <v>0</v>
       </c>
-      <c r="K10">
+      <c r="L10" s="5">
         <v>65.424999999999997</v>
       </c>
-      <c r="L10">
+      <c r="M10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O10" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P10" s="5">
         <v>41.5</v>
       </c>
-      <c r="M10" s="6">
+      <c r="Q10" s="6">
         <v>583.53</v>
       </c>
-      <c r="N10">
+      <c r="R10" s="5">
         <v>17.337499999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="6" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C11" s="6">
         <v>2023</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E11" s="6">
+        <v>12</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F11" s="6">
         <v>2</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="6">
         <v>205</v>
       </c>
-      <c r="G11">
+      <c r="H11" s="5">
         <v>44.5</v>
       </c>
-      <c r="H11">
+      <c r="I11" s="5">
         <v>321.375</v>
       </c>
-      <c r="I11">
+      <c r="J11" s="5">
         <v>21.72</v>
       </c>
-      <c r="J11">
+      <c r="K11" s="5">
         <v>23.11</v>
       </c>
-      <c r="K11">
+      <c r="L11" s="5">
         <v>44.83</v>
       </c>
-      <c r="L11">
+      <c r="M11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O11" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P11" s="5">
         <v>40.5</v>
       </c>
-      <c r="M11" s="6">
+      <c r="Q11" s="6">
         <v>485.35</v>
       </c>
-      <c r="N11">
+      <c r="R11" s="5">
         <v>16.794999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="6" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C12" s="6">
         <v>2023</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="6">
+        <v>12</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F12" s="6">
         <v>3</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="6">
         <v>301</v>
       </c>
-      <c r="G12">
+      <c r="H12" s="5">
         <v>46</v>
       </c>
-      <c r="H12">
+      <c r="I12" s="5">
         <v>269.54000000000002</v>
       </c>
-      <c r="I12">
+      <c r="J12" s="5">
         <v>35.260000000000005</v>
       </c>
-      <c r="J12">
+      <c r="K12" s="5">
         <v>14.13</v>
       </c>
-      <c r="K12">
+      <c r="L12" s="5">
         <v>49.390000000000008</v>
       </c>
-      <c r="L12">
+      <c r="M12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O12" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P12" s="5">
         <v>36.5</v>
       </c>
-      <c r="M12" s="6">
+      <c r="Q12" s="6">
         <v>478.85</v>
       </c>
-      <c r="N12">
+      <c r="R12" s="5">
         <v>17.8475</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="6" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C13" s="6">
         <v>2023</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E13" s="6">
+        <v>13</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F13" s="6">
         <v>3</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="6">
         <v>302</v>
       </c>
-      <c r="G13">
+      <c r="H13" s="5">
         <v>41</v>
       </c>
-      <c r="H13">
+      <c r="I13" s="5">
         <v>346.17499999999995</v>
       </c>
-      <c r="I13">
+      <c r="J13" s="5">
         <v>37.159999999999997</v>
       </c>
-      <c r="J13">
+      <c r="K13" s="5">
         <v>0</v>
       </c>
-      <c r="K13">
+      <c r="L13" s="5">
         <v>37.159999999999997</v>
       </c>
-      <c r="L13">
+      <c r="M13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O13" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P13" s="5">
         <v>37.5</v>
       </c>
-      <c r="M13" s="6">
+      <c r="Q13" s="6">
         <v>481.27</v>
       </c>
-      <c r="N13">
+      <c r="R13" s="5">
         <v>16.892500000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A14" s="6" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C14" s="6">
         <v>2023</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="6">
+        <v>16</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="6">
         <v>3</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <v>303</v>
       </c>
-      <c r="G14">
+      <c r="H14" s="5">
         <v>36.5</v>
       </c>
-      <c r="H14">
+      <c r="I14" s="5">
         <v>266.14</v>
       </c>
-      <c r="I14">
+      <c r="J14" s="5">
         <v>13.940000000000001</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="5">
         <v>14.469999999999999</v>
       </c>
-      <c r="K14">
+      <c r="L14" s="5">
         <v>28.41</v>
       </c>
-      <c r="L14">
+      <c r="M14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N14" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O14">
+        <v>243.02500000000001</v>
+      </c>
+      <c r="P14" s="5">
         <v>27.5</v>
       </c>
-      <c r="M14" s="6">
+      <c r="Q14" s="6">
         <v>495.61</v>
       </c>
-      <c r="N14">
+      <c r="R14" s="5">
         <v>17.692499999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A15" s="6" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C15" s="6">
         <v>2023</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="6">
+        <v>14</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" s="6">
         <v>3</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <v>304</v>
       </c>
-      <c r="G15">
+      <c r="H15" s="5">
         <v>39.5</v>
       </c>
-      <c r="H15">
+      <c r="I15" s="5">
         <v>252</v>
       </c>
-      <c r="I15">
+      <c r="J15" s="5">
         <v>3.37</v>
       </c>
-      <c r="J15">
+      <c r="K15" s="5">
         <v>2.6999999999999997</v>
       </c>
-      <c r="K15">
+      <c r="L15" s="5">
         <v>6.07</v>
       </c>
-      <c r="L15">
+      <c r="M15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N15" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O15">
+        <v>348.44499999999999</v>
+      </c>
+      <c r="P15" s="5">
         <v>35</v>
       </c>
-      <c r="M15" s="6">
+      <c r="Q15" s="6">
         <v>686.07</v>
       </c>
-      <c r="N15">
+      <c r="R15" s="5">
         <v>17.21</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C16" s="6">
         <v>2023</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F16" s="6">
+        <v>3</v>
+      </c>
+      <c r="G16" s="6">
+        <v>305</v>
+      </c>
+      <c r="H16" s="5">
+        <v>38.5</v>
+      </c>
+      <c r="I16" s="5">
+        <v>236.08499999999998</v>
+      </c>
+      <c r="J16" s="5">
+        <v>1.595</v>
+      </c>
+      <c r="K16" s="5">
+        <v>0.73</v>
+      </c>
+      <c r="L16" s="5">
+        <v>2.3250000000000002</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N16" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O16">
+        <v>338.255</v>
+      </c>
+      <c r="P16" s="5">
+        <v>32.5</v>
+      </c>
+      <c r="Q16" s="6">
+        <v>556.48</v>
+      </c>
+      <c r="R16" s="5">
+        <v>16.297499999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="E16" s="6">
-        <v>3</v>
-      </c>
-      <c r="F16" s="6">
-        <v>305</v>
-      </c>
-      <c r="G16">
-        <v>38.5</v>
-      </c>
-      <c r="H16">
-        <v>236.08499999999998</v>
-      </c>
-      <c r="I16">
-        <v>1.595</v>
-      </c>
-      <c r="J16">
-        <v>0.73</v>
-      </c>
-      <c r="K16">
-        <v>2.3250000000000002</v>
-      </c>
-      <c r="L16">
-        <v>32.5</v>
-      </c>
-      <c r="M16" s="6">
-        <v>556.48</v>
-      </c>
-      <c r="N16">
-        <v>16.297499999999999</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A17" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B17" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C17" s="6">
         <v>2023</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E17" s="6">
+        <v>16</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F17" s="6">
         <v>4</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <v>401</v>
       </c>
-      <c r="G17">
+      <c r="H17" s="5">
         <v>43.5</v>
       </c>
-      <c r="H17">
+      <c r="I17" s="5">
         <v>328.995</v>
       </c>
-      <c r="I17">
+      <c r="J17" s="5">
         <v>13.18</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="5">
         <v>2.7050000000000001</v>
       </c>
-      <c r="K17">
+      <c r="L17" s="5">
         <v>15.885</v>
       </c>
-      <c r="L17">
+      <c r="M17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N17" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O17">
+        <v>261.685</v>
+      </c>
+      <c r="P17" s="5">
         <v>40.5</v>
       </c>
-      <c r="M17" s="6">
+      <c r="Q17" s="6">
         <v>575.66999999999996</v>
       </c>
-      <c r="N17">
+      <c r="R17" s="5">
         <v>18.105</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C18" s="6">
         <v>2023</v>
       </c>
       <c r="D18" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F18" s="6">
+        <v>4</v>
+      </c>
+      <c r="G18" s="6">
+        <v>402</v>
+      </c>
+      <c r="H18" s="5">
+        <v>36</v>
+      </c>
+      <c r="I18" s="5">
+        <v>269.745</v>
+      </c>
+      <c r="J18" s="5">
+        <v>1.155</v>
+      </c>
+      <c r="K18" s="5">
+        <v>10.41</v>
+      </c>
+      <c r="L18" s="5">
+        <v>11.565</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N18" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O18">
+        <v>236.04500000000002</v>
+      </c>
+      <c r="P18" s="5">
+        <v>34.5</v>
+      </c>
+      <c r="Q18" s="6">
+        <v>457.43</v>
+      </c>
+      <c r="R18" s="5">
+        <v>16.692499999999999</v>
+      </c>
+    </row>
+    <row r="19" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="6" t="s">
         <v>19</v>
-      </c>
-      <c r="E18" s="6">
-        <v>4</v>
-      </c>
-      <c r="F18" s="6">
-        <v>402</v>
-      </c>
-      <c r="G18">
-        <v>36</v>
-      </c>
-      <c r="H18">
-        <v>269.745</v>
-      </c>
-      <c r="I18">
-        <v>1.155</v>
-      </c>
-      <c r="J18">
-        <v>10.41</v>
-      </c>
-      <c r="K18">
-        <v>11.565</v>
-      </c>
-      <c r="L18">
-        <v>34.5</v>
-      </c>
-      <c r="M18" s="6">
-        <v>457.43</v>
-      </c>
-      <c r="N18">
-        <v>16.692499999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>40</v>
       </c>
       <c r="C19" s="6">
         <v>2023</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E19" s="6">
+        <v>14</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F19" s="6">
         <v>4</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="6">
         <v>403</v>
       </c>
-      <c r="G19">
+      <c r="H19" s="5">
         <v>36</v>
       </c>
-      <c r="H19">
+      <c r="I19" s="5">
         <v>211.89</v>
       </c>
-      <c r="I19">
+      <c r="J19" s="5">
         <v>7.67</v>
       </c>
-      <c r="J19">
+      <c r="K19" s="5">
         <v>9.1649999999999991</v>
       </c>
-      <c r="K19">
+      <c r="L19" s="5">
         <v>16.835000000000001</v>
       </c>
-      <c r="L19">
+      <c r="M19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O19">
+        <v>230.035</v>
+      </c>
+      <c r="P19" s="5">
         <v>39</v>
       </c>
-      <c r="M19" s="6">
+      <c r="Q19" s="6">
         <v>549.80999999999995</v>
       </c>
-      <c r="N19">
+      <c r="R19" s="5">
         <v>16.734999999999999</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C20" s="6">
         <v>2023</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E20" s="6">
+        <v>13</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F20" s="6">
         <v>4</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="6">
         <v>404</v>
       </c>
-      <c r="G20">
+      <c r="H20" s="5">
         <v>45.5</v>
       </c>
-      <c r="H20">
+      <c r="I20" s="5">
         <v>245.54</v>
       </c>
-      <c r="I20">
+      <c r="J20" s="5">
         <v>36.414999999999999</v>
       </c>
-      <c r="J20">
+      <c r="K20" s="5">
         <v>0.05</v>
       </c>
-      <c r="K20">
+      <c r="L20" s="5">
         <v>36.464999999999996</v>
       </c>
-      <c r="L20">
+      <c r="M20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O20" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P20" s="5">
         <v>41.5</v>
       </c>
-      <c r="M20" s="6">
+      <c r="Q20" s="6">
         <v>487.11</v>
       </c>
-      <c r="N20">
+      <c r="R20" s="5">
         <v>17.310000000000002</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="C21" s="6">
         <v>2023</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E21" s="6">
+        <v>12</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F21" s="6">
         <v>4</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="6">
         <v>405</v>
       </c>
-      <c r="G21">
+      <c r="H21" s="5">
         <v>43</v>
       </c>
-      <c r="H21">
+      <c r="I21" s="5">
         <v>199.87</v>
       </c>
-      <c r="I21">
+      <c r="J21" s="5">
         <v>56.46</v>
       </c>
-      <c r="J21">
+      <c r="K21" s="5">
         <v>22.7</v>
       </c>
-      <c r="K21">
+      <c r="L21" s="5">
         <v>79.16</v>
       </c>
-      <c r="L21">
+      <c r="M21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O21" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P21" s="5">
         <v>43.5</v>
       </c>
-      <c r="M21">
+      <c r="Q21" s="5">
         <v>434.21</v>
       </c>
-      <c r="N21">
+      <c r="R21" s="5">
         <v>17.059999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="6" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C22" s="6">
         <v>2024</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E22" s="6">
+        <v>12</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F22" s="6">
         <v>1</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="6">
         <v>101</v>
       </c>
-      <c r="G22">
+      <c r="H22" s="5">
         <v>47.5</v>
       </c>
-      <c r="H22">
+      <c r="I22" s="5">
         <v>508.65499999999997</v>
       </c>
-      <c r="I22">
+      <c r="J22" s="5">
         <v>2.0550000000000002</v>
       </c>
-      <c r="J22">
+      <c r="K22" s="5">
         <v>10.035</v>
       </c>
-      <c r="K22">
+      <c r="L22" s="5">
         <v>12.09</v>
       </c>
-      <c r="L22">
+      <c r="M22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O22" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P22" s="5">
         <v>45.5</v>
       </c>
-      <c r="M22" s="6">
+      <c r="Q22" s="6">
         <v>612</v>
       </c>
-      <c r="N22">
+      <c r="R22" s="5">
         <v>19.122500000000002</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="6" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C23" s="6">
         <v>2024</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="6">
+        <v>13</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F23" s="6">
         <v>1</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="6">
         <v>102</v>
       </c>
-      <c r="G23">
+      <c r="H23" s="5">
         <v>47.5</v>
       </c>
-      <c r="H23">
+      <c r="I23" s="5">
         <v>503.56</v>
       </c>
-      <c r="I23">
+      <c r="J23" s="5">
         <v>0</v>
       </c>
-      <c r="J23">
+      <c r="K23" s="5">
         <v>0</v>
       </c>
-      <c r="K23">
+      <c r="L23" s="5">
         <v>0</v>
       </c>
-      <c r="L23">
+      <c r="M23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O23" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P23" s="5">
         <v>47.5</v>
       </c>
-      <c r="M23" s="6">
+      <c r="Q23" s="6">
         <v>790</v>
       </c>
-      <c r="N23">
+      <c r="R23" s="5">
         <v>19.29</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="6" t="s">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C24" s="6">
         <v>2024</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E24" s="6">
+        <v>14</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="6">
         <v>1</v>
       </c>
-      <c r="F24" s="6">
+      <c r="G24" s="6">
         <v>103</v>
       </c>
-      <c r="G24">
+      <c r="H24" s="5">
         <v>44.5</v>
       </c>
-      <c r="H24">
+      <c r="I24" s="5">
         <v>378.02499999999998</v>
       </c>
-      <c r="I24">
+      <c r="J24" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J24">
+      <c r="K24" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="K24">
+      <c r="L24" s="5">
         <v>0.05</v>
       </c>
-      <c r="L24">
+      <c r="M24">
+        <v>45.115000000000002</v>
+      </c>
+      <c r="N24">
+        <v>146.14499999999998</v>
+      </c>
+      <c r="O24">
+        <v>191.26</v>
+      </c>
+      <c r="P24" s="5">
         <v>44</v>
       </c>
-      <c r="M24" s="6">
+      <c r="Q24" s="6">
         <v>641</v>
       </c>
-      <c r="N24">
+      <c r="R24" s="5">
         <v>18.079999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="6" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C25" s="6">
         <v>2024</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E25" s="6">
+        <v>15</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F25" s="6">
         <v>1</v>
       </c>
-      <c r="F25" s="6">
+      <c r="G25" s="6">
         <v>104</v>
       </c>
-      <c r="G25">
+      <c r="H25" s="5">
         <v>40</v>
       </c>
-      <c r="H25">
+      <c r="I25" s="5">
         <v>423.45</v>
       </c>
-      <c r="I25">
+      <c r="J25" s="5">
         <v>0</v>
       </c>
-      <c r="J25">
+      <c r="K25" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="K25">
+      <c r="L25" s="5">
         <v>9.5000000000000001E-2</v>
       </c>
-      <c r="L25">
+      <c r="M25">
+        <v>36.64</v>
+      </c>
+      <c r="N25">
+        <v>212.19</v>
+      </c>
+      <c r="O25">
+        <v>248.82999999999998</v>
+      </c>
+      <c r="P25" s="5">
         <v>46</v>
       </c>
-      <c r="M25" s="6">
+      <c r="Q25" s="6">
         <v>660</v>
       </c>
-      <c r="N25">
+      <c r="R25" s="5">
         <v>18.2425</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>37</v>
       </c>
       <c r="C26" s="6">
         <v>2024</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E26" s="6">
+        <v>16</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="6">
         <v>1</v>
       </c>
-      <c r="F26" s="6">
+      <c r="G26" s="6">
         <v>105</v>
       </c>
-      <c r="G26">
+      <c r="H26" s="5">
         <v>40</v>
       </c>
-      <c r="H26">
+      <c r="I26" s="5">
         <v>414.125</v>
       </c>
-      <c r="I26">
+      <c r="J26" s="5">
         <v>0</v>
       </c>
-      <c r="J26">
+      <c r="K26" s="5">
         <v>0</v>
       </c>
-      <c r="K26">
+      <c r="L26" s="5">
         <v>0</v>
       </c>
-      <c r="L26">
+      <c r="M26">
+        <v>69.954999999999998</v>
+      </c>
+      <c r="N26">
+        <v>178.73000000000002</v>
+      </c>
+      <c r="O26">
+        <v>248.685</v>
+      </c>
+      <c r="P26" s="5">
         <v>46.5</v>
       </c>
-      <c r="M26" s="6">
+      <c r="Q26" s="6">
         <v>624</v>
       </c>
-      <c r="N26">
+      <c r="R26" s="5">
         <v>17.77</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="6" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C27" s="6">
         <v>2024</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E27" s="6">
+        <v>16</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F27" s="6">
         <v>2</v>
       </c>
-      <c r="F27" s="6">
+      <c r="G27" s="6">
         <v>201</v>
       </c>
-      <c r="G27">
+      <c r="H27" s="5">
         <v>47.5</v>
       </c>
-      <c r="H27">
+      <c r="I27" s="5">
         <v>415.09500000000003</v>
       </c>
-      <c r="I27">
+      <c r="J27" s="5">
         <v>0</v>
       </c>
-      <c r="J27">
+      <c r="K27" s="5">
         <v>0</v>
       </c>
-      <c r="K27">
+      <c r="L27" s="5">
         <v>0</v>
       </c>
-      <c r="L27">
+      <c r="M27">
+        <v>64.38</v>
+      </c>
+      <c r="N27">
+        <v>193.20499999999998</v>
+      </c>
+      <c r="O27">
+        <v>257.58499999999998</v>
+      </c>
+      <c r="P27" s="5">
         <v>45</v>
       </c>
-      <c r="M27" s="6">
+      <c r="Q27" s="6">
         <v>670</v>
       </c>
-      <c r="N27">
+      <c r="R27" s="5">
         <v>18.309999999999999</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="6" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C28" s="6">
         <v>2024</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E28" s="6">
+        <v>15</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F28" s="6">
         <v>2</v>
       </c>
-      <c r="F28" s="6">
+      <c r="G28" s="6">
         <v>202</v>
       </c>
-      <c r="G28">
+      <c r="H28" s="5">
         <v>43</v>
       </c>
-      <c r="H28">
+      <c r="I28" s="5">
         <v>437.875</v>
       </c>
-      <c r="I28">
+      <c r="J28" s="5">
         <v>0</v>
       </c>
-      <c r="J28">
+      <c r="K28" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="K28">
+      <c r="L28" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="L28">
+      <c r="M28">
+        <v>57.83</v>
+      </c>
+      <c r="N28">
+        <v>140.92000000000002</v>
+      </c>
+      <c r="O28">
+        <v>198.75</v>
+      </c>
+      <c r="P28" s="5">
         <v>43.5</v>
       </c>
-      <c r="M28" s="6">
+      <c r="Q28" s="6">
         <v>638</v>
       </c>
-      <c r="N28">
+      <c r="R28" s="5">
         <v>18.704999999999998</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="6" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C29" s="6">
         <v>2024</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E29" s="6">
+        <v>14</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F29" s="6">
         <v>2</v>
       </c>
-      <c r="F29" s="6">
+      <c r="G29" s="6">
         <v>203</v>
       </c>
-      <c r="G29">
+      <c r="H29" s="5">
         <v>41.5</v>
       </c>
-      <c r="H29">
+      <c r="I29" s="5">
         <v>409.44500000000005</v>
       </c>
-      <c r="I29">
+      <c r="J29" s="5">
         <v>0</v>
       </c>
-      <c r="J29">
+      <c r="K29" s="5">
         <v>0.18</v>
       </c>
-      <c r="K29">
+      <c r="L29" s="5">
         <v>0.18</v>
       </c>
-      <c r="L29">
+      <c r="M29">
+        <v>51.82</v>
+      </c>
+      <c r="N29">
+        <v>128.94</v>
+      </c>
+      <c r="O29">
+        <v>180.76</v>
+      </c>
+      <c r="P29" s="5">
         <v>44</v>
       </c>
-      <c r="M29" s="6">
+      <c r="Q29" s="6">
         <v>646</v>
       </c>
-      <c r="N29">
+      <c r="R29" s="5">
         <v>17.9375</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="6" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C30" s="6">
         <v>2024</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="6">
+        <v>13</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="6">
         <v>2</v>
       </c>
-      <c r="F30" s="6">
+      <c r="G30" s="6">
         <v>204</v>
       </c>
-      <c r="G30">
+      <c r="H30" s="5">
         <v>47</v>
       </c>
-      <c r="H30">
+      <c r="I30" s="5">
         <v>481.32499999999999</v>
       </c>
-      <c r="I30">
+      <c r="J30" s="5">
         <v>8.5000000000000006E-2</v>
       </c>
-      <c r="J30">
+      <c r="K30" s="5">
         <v>0.02</v>
       </c>
-      <c r="K30">
+      <c r="L30" s="5">
         <v>0.10500000000000001</v>
       </c>
-      <c r="L30">
+      <c r="M30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O30" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P30" s="5">
         <v>49</v>
       </c>
-      <c r="M30" s="6">
+      <c r="Q30" s="6">
         <v>662</v>
       </c>
-      <c r="N30">
+      <c r="R30" s="5">
         <v>18.942499999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="6" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C31" s="6">
         <v>2024</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E31" s="6">
+        <v>12</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F31" s="6">
         <v>2</v>
       </c>
-      <c r="F31" s="6">
+      <c r="G31" s="6">
         <v>205</v>
       </c>
-      <c r="G31">
+      <c r="H31" s="5">
         <v>46</v>
       </c>
-      <c r="H31">
+      <c r="I31" s="5">
         <v>417.31</v>
       </c>
-      <c r="I31">
+      <c r="J31" s="5">
         <v>3.0649999999999999</v>
       </c>
-      <c r="J31">
+      <c r="K31" s="5">
         <v>9.01</v>
       </c>
-      <c r="K31">
+      <c r="L31" s="5">
         <v>12.074999999999999</v>
       </c>
-      <c r="L31">
+      <c r="M31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O31" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P31" s="5">
         <v>46</v>
       </c>
-      <c r="M31" s="6">
+      <c r="Q31" s="6">
         <v>644</v>
       </c>
-      <c r="N31">
+      <c r="R31" s="5">
         <v>18.369999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="6" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C32" s="6">
         <v>2024</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E32" s="6">
+        <v>12</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F32" s="6">
         <v>3</v>
       </c>
-      <c r="F32" s="6">
+      <c r="G32" s="6">
         <v>301</v>
       </c>
-      <c r="G32">
+      <c r="H32" s="5">
         <v>47.5</v>
       </c>
-      <c r="H32">
+      <c r="I32" s="5">
         <v>456.25</v>
       </c>
-      <c r="I32">
+      <c r="J32" s="5">
         <v>4.42</v>
       </c>
-      <c r="J32">
+      <c r="K32" s="5">
         <v>6.5250000000000004</v>
       </c>
-      <c r="K32">
+      <c r="L32" s="5">
         <v>10.945</v>
       </c>
-      <c r="L32">
+      <c r="M32" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N32" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O32" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P32" s="5">
         <v>37</v>
       </c>
-      <c r="M32" s="6">
+      <c r="Q32" s="6">
         <v>588</v>
       </c>
-      <c r="N32">
+      <c r="R32" s="5">
         <v>17.094999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="6" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C33" s="6">
         <v>2024</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="6">
+        <v>13</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F33" s="6">
         <v>3</v>
       </c>
-      <c r="F33" s="6">
+      <c r="G33" s="6">
         <v>302</v>
       </c>
-      <c r="G33">
+      <c r="H33" s="5">
         <v>41.5</v>
       </c>
-      <c r="H33">
+      <c r="I33" s="5">
         <v>496.08500000000004</v>
       </c>
-      <c r="I33">
+      <c r="J33" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J33">
+      <c r="K33" s="5">
         <v>0</v>
       </c>
-      <c r="K33">
+      <c r="L33" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="L33">
+      <c r="M33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O33" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P33" s="5">
         <v>38.5</v>
       </c>
-      <c r="M33" s="6">
+      <c r="Q33" s="6">
         <v>676</v>
       </c>
-      <c r="N33">
+      <c r="R33" s="5">
         <v>19.395</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="6" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C34" s="6">
         <v>2024</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E34" s="6">
+        <v>16</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F34" s="6">
         <v>3</v>
       </c>
-      <c r="F34" s="6">
+      <c r="G34" s="6">
         <v>303</v>
       </c>
-      <c r="G34">
+      <c r="H34" s="5">
         <v>53.5</v>
       </c>
-      <c r="H34">
+      <c r="I34" s="5">
         <v>342.25</v>
       </c>
-      <c r="I34">
+      <c r="J34" s="5">
         <v>10.765000000000001</v>
       </c>
-      <c r="J34">
+      <c r="K34" s="5">
         <v>6.5</v>
       </c>
-      <c r="K34">
+      <c r="L34" s="5">
         <v>17.265000000000001</v>
       </c>
-      <c r="L34">
+      <c r="M34">
+        <v>38.650000000000006</v>
+      </c>
+      <c r="N34">
+        <v>184.41499999999999</v>
+      </c>
+      <c r="O34">
+        <v>223.065</v>
+      </c>
+      <c r="P34" s="5">
         <v>44.5</v>
       </c>
-      <c r="M34" s="6">
+      <c r="Q34" s="6">
         <v>672</v>
       </c>
-      <c r="N34">
+      <c r="R34" s="5">
         <v>19.012499999999999</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="6" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C35" s="6">
         <v>2024</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E35" s="6">
+        <v>14</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F35" s="6">
         <v>3</v>
       </c>
-      <c r="F35" s="6">
+      <c r="G35" s="6">
         <v>304</v>
       </c>
-      <c r="G35">
+      <c r="H35" s="5">
         <v>54</v>
       </c>
-      <c r="H35">
+      <c r="I35" s="5">
         <v>371.88</v>
       </c>
-      <c r="I35">
+      <c r="J35" s="5">
         <v>12.455</v>
       </c>
-      <c r="J35">
+      <c r="K35" s="5">
         <v>2.1850000000000001</v>
       </c>
-      <c r="K35">
+      <c r="L35" s="5">
         <v>14.64</v>
       </c>
-      <c r="L35">
+      <c r="M35">
+        <v>39.164999999999999</v>
+      </c>
+      <c r="N35">
+        <v>113.44499999999999</v>
+      </c>
+      <c r="O35">
+        <v>152.61000000000001</v>
+      </c>
+      <c r="P35" s="5">
         <v>46</v>
       </c>
-      <c r="M35" s="6">
+      <c r="Q35" s="6">
         <v>604</v>
       </c>
-      <c r="N35">
+      <c r="R35" s="5">
         <v>19.022500000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="6" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C36" s="6">
         <v>2024</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E36" s="6">
+        <v>15</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F36" s="6">
         <v>3</v>
       </c>
-      <c r="F36" s="6">
+      <c r="G36" s="6">
         <v>305</v>
       </c>
-      <c r="G36">
+      <c r="H36" s="5">
         <v>42.5</v>
       </c>
-      <c r="H36">
+      <c r="I36" s="5">
         <v>374.745</v>
       </c>
-      <c r="I36">
+      <c r="J36" s="5">
         <v>5.29</v>
       </c>
-      <c r="J36">
+      <c r="K36" s="5">
         <v>40.31</v>
       </c>
-      <c r="K36">
+      <c r="L36" s="5">
         <v>45.6</v>
       </c>
-      <c r="L36">
+      <c r="M36">
+        <v>22.09</v>
+      </c>
+      <c r="N36">
+        <v>101.10499999999999</v>
+      </c>
+      <c r="O36">
+        <v>123.19499999999999</v>
+      </c>
+      <c r="P36" s="5">
         <v>48.5</v>
       </c>
-      <c r="M36" s="6">
+      <c r="Q36" s="6">
         <v>586</v>
       </c>
-      <c r="N36">
+      <c r="R36" s="5">
         <v>17.952500000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="6" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C37" s="6">
         <v>2024</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E37" s="6">
+        <v>16</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F37" s="6">
         <v>4</v>
       </c>
-      <c r="F37" s="6">
+      <c r="G37" s="6">
         <v>401</v>
       </c>
-      <c r="G37">
+      <c r="H37" s="5">
         <v>42</v>
       </c>
-      <c r="H37">
+      <c r="I37" s="5">
         <v>322.3</v>
       </c>
-      <c r="I37">
+      <c r="J37" s="5">
         <v>0.77499999999999991</v>
       </c>
-      <c r="J37">
+      <c r="K37" s="5">
         <v>36.409999999999997</v>
       </c>
-      <c r="K37">
+      <c r="L37" s="5">
         <v>37.184999999999995</v>
       </c>
-      <c r="L37">
+      <c r="M37">
+        <v>51.61</v>
+      </c>
+      <c r="N37">
+        <v>57.82</v>
+      </c>
+      <c r="O37">
+        <v>109.43</v>
+      </c>
+      <c r="P37" s="5">
         <v>39.5</v>
       </c>
-      <c r="M37" s="6">
+      <c r="Q37" s="6">
         <v>534</v>
       </c>
-      <c r="N37">
+      <c r="R37" s="5">
         <v>18.0975</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="6" t="s">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C38" s="6">
         <v>2024</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E38" s="6">
+        <v>15</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F38" s="6">
         <v>4</v>
       </c>
-      <c r="F38" s="6">
+      <c r="G38" s="6">
         <v>402</v>
       </c>
-      <c r="G38">
+      <c r="H38" s="5">
         <v>43.5</v>
       </c>
-      <c r="H38">
+      <c r="I38" s="5">
         <v>359.185</v>
       </c>
-      <c r="I38">
+      <c r="J38" s="5">
         <v>0</v>
       </c>
-      <c r="J38">
+      <c r="K38" s="5">
         <v>3.7199999999999998</v>
       </c>
-      <c r="K38">
+      <c r="L38" s="5">
         <v>3.7199999999999998</v>
       </c>
-      <c r="L38">
+      <c r="M38">
+        <v>24.2</v>
+      </c>
+      <c r="N38">
+        <v>135.565</v>
+      </c>
+      <c r="O38">
+        <v>159.76499999999999</v>
+      </c>
+      <c r="P38" s="5">
         <v>44.5</v>
       </c>
-      <c r="M38" s="6">
+      <c r="Q38" s="6">
         <v>548</v>
       </c>
-      <c r="N38">
+      <c r="R38" s="5">
         <v>18.079999999999998</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="6" t="s">
-        <v>34</v>
+        <v>59</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C39" s="6">
         <v>2024</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E39" s="6">
+        <v>14</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F39" s="6">
         <v>4</v>
       </c>
-      <c r="F39" s="6">
+      <c r="G39" s="6">
         <v>403</v>
       </c>
-      <c r="G39">
+      <c r="H39" s="5">
         <v>44.5</v>
       </c>
-      <c r="H39">
+      <c r="I39" s="5">
         <v>359.38</v>
       </c>
-      <c r="I39">
+      <c r="J39" s="5">
         <v>0.52500000000000002</v>
       </c>
-      <c r="J39">
+      <c r="K39" s="5">
         <v>2.16</v>
       </c>
-      <c r="K39">
+      <c r="L39" s="5">
         <v>2.6850000000000001</v>
       </c>
-      <c r="L39">
+      <c r="M39">
+        <v>33.239999999999995</v>
+      </c>
+      <c r="N39">
+        <v>133.69</v>
+      </c>
+      <c r="O39">
+        <v>166.93</v>
+      </c>
+      <c r="P39" s="5">
         <v>38</v>
       </c>
-      <c r="M39" s="6">
+      <c r="Q39" s="6">
         <v>586</v>
       </c>
-      <c r="N39">
+      <c r="R39" s="5">
         <v>18.052500000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A40" s="6" t="s">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C40" s="6">
         <v>2024</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E40" s="6">
+        <v>13</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F40" s="6">
         <v>4</v>
       </c>
-      <c r="F40" s="6">
+      <c r="G40" s="6">
         <v>404</v>
       </c>
-      <c r="G40">
+      <c r="H40" s="5">
         <v>45</v>
       </c>
-      <c r="H40">
+      <c r="I40" s="5">
         <v>428</v>
       </c>
-      <c r="I40">
+      <c r="J40" s="5">
         <v>2.23</v>
       </c>
-      <c r="J40">
+      <c r="K40" s="5">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="K40">
+      <c r="L40" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L40">
+      <c r="M40" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N40" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O40" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P40" s="5">
         <v>50</v>
       </c>
-      <c r="M40" s="6">
+      <c r="Q40" s="6">
         <v>678</v>
       </c>
-      <c r="N40">
+      <c r="R40" s="5">
         <v>18.952500000000001</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A41" s="6" t="s">
-        <v>36</v>
+        <v>61</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C41" s="6">
         <v>2024</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E41" s="6">
+        <v>12</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="6">
         <v>4</v>
       </c>
-      <c r="F41" s="6">
+      <c r="G41" s="6">
         <v>405</v>
       </c>
-      <c r="G41">
+      <c r="H41" s="5">
         <v>50</v>
       </c>
-      <c r="H41">
+      <c r="I41" s="5">
         <v>470.08499999999998</v>
       </c>
-      <c r="I41">
+      <c r="J41" s="5">
         <v>0.255</v>
       </c>
-      <c r="J41">
+      <c r="K41" s="5">
         <v>3.6349999999999998</v>
       </c>
-      <c r="K41">
+      <c r="L41" s="5">
         <v>3.8899999999999997</v>
       </c>
-      <c r="L41">
+      <c r="M41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O41" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P41" s="5">
         <v>45.5</v>
       </c>
-      <c r="M41">
+      <c r="Q41" s="5">
         <v>660</v>
       </c>
-      <c r="N41">
+      <c r="R41" s="5">
         <v>18.532499999999999</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A42" s="6" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C42" s="6">
         <v>2024</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E42" s="6">
+        <v>12</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F42" s="6">
         <v>1</v>
       </c>
-      <c r="F42" s="6">
+      <c r="G42" s="6">
         <v>101</v>
       </c>
-      <c r="G42">
+      <c r="H42" s="5">
         <v>51.5</v>
       </c>
-      <c r="H42" s="7">
+      <c r="I42" s="7">
         <v>476.20499999999998</v>
       </c>
-      <c r="I42">
+      <c r="J42" s="5">
         <v>0.70500000000000007</v>
       </c>
-      <c r="J42">
+      <c r="K42" s="5">
         <v>1.76</v>
       </c>
-      <c r="K42">
+      <c r="L42" s="5">
         <v>2.4649999999999999</v>
       </c>
-      <c r="L42">
+      <c r="M42" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N42" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O42" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P42" s="5">
         <v>44.5</v>
       </c>
-      <c r="M42" s="6">
+      <c r="Q42" s="6">
         <v>724</v>
       </c>
-      <c r="N42">
+      <c r="R42" s="5">
         <v>18.305</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A43" s="6" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C43" s="6">
         <v>2024</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E43" s="6">
+        <v>13</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F43" s="6">
         <v>1</v>
       </c>
-      <c r="F43" s="6">
+      <c r="G43" s="6">
         <v>102</v>
       </c>
-      <c r="G43">
+      <c r="H43" s="5">
         <v>49.5</v>
       </c>
-      <c r="H43" s="7">
+      <c r="I43" s="7">
         <v>447.4</v>
       </c>
-      <c r="I43">
+      <c r="J43" s="5">
         <v>0.62</v>
       </c>
-      <c r="J43">
+      <c r="K43" s="5">
         <v>0</v>
       </c>
-      <c r="K43">
+      <c r="L43" s="5">
         <v>0.62</v>
       </c>
-      <c r="L43">
+      <c r="M43" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N43" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O43" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P43" s="5">
         <v>47.5</v>
       </c>
-      <c r="M43" s="6">
+      <c r="Q43" s="6">
         <v>690</v>
       </c>
-      <c r="N43">
+      <c r="R43" s="5">
         <v>19.094999999999999</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A44" s="6" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C44" s="6">
         <v>2024</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E44" s="6">
+        <v>14</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F44" s="6">
         <v>1</v>
       </c>
-      <c r="F44" s="6">
+      <c r="G44" s="6">
         <v>103</v>
       </c>
-      <c r="G44">
+      <c r="H44" s="5">
         <v>43</v>
       </c>
-      <c r="H44" s="7">
+      <c r="I44" s="7">
         <v>390.67</v>
       </c>
-      <c r="I44">
+      <c r="J44" s="5">
         <v>0</v>
       </c>
-      <c r="J44">
+      <c r="K44" s="5">
         <v>0.45</v>
       </c>
-      <c r="K44">
+      <c r="L44" s="5">
         <v>0.45</v>
       </c>
-      <c r="L44">
+      <c r="M44">
+        <v>48.344999999999999</v>
+      </c>
+      <c r="N44">
+        <v>224.59</v>
+      </c>
+      <c r="O44">
+        <v>272.935</v>
+      </c>
+      <c r="P44" s="5">
         <v>36.5</v>
       </c>
-      <c r="M44" s="6">
+      <c r="Q44" s="6">
         <v>638</v>
       </c>
-      <c r="N44">
+      <c r="R44" s="5">
         <v>17.587500000000002</v>
       </c>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A45" s="6" t="s">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C45" s="6">
         <v>2024</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E45" s="6">
+        <v>15</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F45" s="6">
         <v>1</v>
       </c>
-      <c r="F45" s="6">
+      <c r="G45" s="6">
         <v>104</v>
       </c>
-      <c r="G45">
+      <c r="H45" s="5">
         <v>45.5</v>
       </c>
-      <c r="H45" s="7">
+      <c r="I45" s="7">
         <v>410.72500000000002</v>
       </c>
-      <c r="I45">
+      <c r="J45" s="5">
         <v>0</v>
       </c>
-      <c r="J45">
+      <c r="K45" s="5">
         <v>0</v>
       </c>
-      <c r="K45">
+      <c r="L45" s="5">
         <v>0</v>
       </c>
-      <c r="L45">
+      <c r="M45">
+        <v>90.1</v>
+      </c>
+      <c r="N45">
+        <v>197.71</v>
+      </c>
+      <c r="O45">
+        <v>287.81</v>
+      </c>
+      <c r="P45" s="5">
         <v>49</v>
       </c>
-      <c r="M45" s="6">
+      <c r="Q45" s="6">
         <v>662</v>
       </c>
-      <c r="N45">
+      <c r="R45" s="5">
         <v>17.649999999999999</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A46" s="6" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="B46" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C46" s="6">
         <v>2024</v>
       </c>
       <c r="D46" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F46" s="6">
+        <v>1</v>
+      </c>
+      <c r="G46" s="6">
+        <v>105</v>
+      </c>
+      <c r="H46" s="5">
+        <v>38.5</v>
+      </c>
+      <c r="I46" s="7">
+        <v>357.96499999999997</v>
+      </c>
+      <c r="J46" s="5">
+        <v>0</v>
+      </c>
+      <c r="K46" s="5">
+        <v>0</v>
+      </c>
+      <c r="L46" s="5">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>65.064999999999998</v>
+      </c>
+      <c r="N46">
+        <v>233.64499999999998</v>
+      </c>
+      <c r="O46">
+        <v>298.70999999999998</v>
+      </c>
+      <c r="P46" s="5">
+        <v>46.5</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>700</v>
+      </c>
+      <c r="R46" s="5">
+        <v>17.990000000000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A47" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B47" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="E46" s="6">
-        <v>1</v>
-      </c>
-      <c r="F46" s="6">
-        <v>105</v>
-      </c>
-      <c r="G46">
-        <v>38.5</v>
-      </c>
-      <c r="H46" s="7">
-        <v>357.96499999999997</v>
-      </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>0</v>
-      </c>
-      <c r="L46">
-        <v>46.5</v>
-      </c>
-      <c r="M46" s="6">
-        <v>700</v>
-      </c>
-      <c r="N46">
-        <v>17.990000000000002</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C47" s="6">
         <v>2024</v>
       </c>
       <c r="D47" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F47" s="6">
+        <v>2</v>
+      </c>
+      <c r="G47" s="6">
+        <v>201</v>
+      </c>
+      <c r="H47" s="5">
+        <v>46.5</v>
+      </c>
+      <c r="I47" s="7">
+        <v>423.77499999999998</v>
+      </c>
+      <c r="J47" s="5">
+        <v>0</v>
+      </c>
+      <c r="K47" s="5">
+        <v>0</v>
+      </c>
+      <c r="L47" s="5">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>89.66</v>
+      </c>
+      <c r="N47">
+        <v>242.38499999999999</v>
+      </c>
+      <c r="O47">
+        <v>332.04500000000002</v>
+      </c>
+      <c r="P47" s="5">
+        <v>46</v>
+      </c>
+      <c r="Q47" s="6">
+        <v>626</v>
+      </c>
+      <c r="R47" s="5">
+        <v>18.3125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A48" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="E47" s="6">
-        <v>2</v>
-      </c>
-      <c r="F47" s="6">
-        <v>201</v>
-      </c>
-      <c r="G47">
-        <v>46.5</v>
-      </c>
-      <c r="H47" s="7">
-        <v>423.77499999999998</v>
-      </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>0</v>
-      </c>
-      <c r="L47">
-        <v>46</v>
-      </c>
-      <c r="M47" s="6">
-        <v>626</v>
-      </c>
-      <c r="N47">
-        <v>18.3125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C48" s="6">
         <v>2024</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E48" s="6">
+        <v>15</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F48" s="6">
         <v>2</v>
       </c>
-      <c r="F48" s="6">
+      <c r="G48" s="6">
         <v>202</v>
       </c>
-      <c r="G48">
+      <c r="H48" s="5">
         <v>43.5</v>
       </c>
-      <c r="H48" s="7">
+      <c r="I48" s="7">
         <v>393.08499999999998</v>
       </c>
-      <c r="I48">
+      <c r="J48" s="5">
         <v>0</v>
       </c>
-      <c r="J48">
+      <c r="K48" s="5">
         <v>0</v>
       </c>
-      <c r="K48">
+      <c r="L48" s="5">
         <v>0</v>
       </c>
-      <c r="L48">
+      <c r="M48">
+        <v>88.155000000000001</v>
+      </c>
+      <c r="N48">
+        <v>299.19</v>
+      </c>
+      <c r="O48">
+        <v>387.34499999999997</v>
+      </c>
+      <c r="P48" s="5">
         <v>44</v>
       </c>
-      <c r="M48" s="6">
+      <c r="Q48" s="6">
         <v>686</v>
       </c>
-      <c r="N48">
+      <c r="R48" s="5">
         <v>17.740000000000002</v>
       </c>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A49" s="6" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C49" s="6">
         <v>2024</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E49" s="6">
+        <v>14</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F49" s="6">
         <v>2</v>
       </c>
-      <c r="F49" s="6">
+      <c r="G49" s="6">
         <v>203</v>
       </c>
-      <c r="G49">
+      <c r="H49" s="5">
         <v>43</v>
       </c>
-      <c r="H49" s="7">
+      <c r="I49" s="7">
         <v>426.2</v>
       </c>
-      <c r="I49">
+      <c r="J49" s="5">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="J49">
+      <c r="K49" s="5">
         <v>0.28000000000000003</v>
       </c>
-      <c r="K49">
+      <c r="L49" s="5">
         <v>0.30500000000000005</v>
       </c>
-      <c r="L49">
+      <c r="M49">
+        <v>56.895000000000003</v>
+      </c>
+      <c r="N49">
+        <v>185.99</v>
+      </c>
+      <c r="O49">
+        <v>242.88499999999999</v>
+      </c>
+      <c r="P49" s="5">
         <v>47</v>
       </c>
-      <c r="M49" s="6">
+      <c r="Q49" s="6">
         <v>690</v>
       </c>
-      <c r="N49">
+      <c r="R49" s="5">
         <v>18.169999999999998</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A50" s="6" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C50" s="6">
         <v>2024</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="6">
+        <v>13</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F50" s="6">
         <v>2</v>
       </c>
-      <c r="F50" s="6">
+      <c r="G50" s="6">
         <v>204</v>
       </c>
-      <c r="G50">
+      <c r="H50" s="5">
         <v>51.5</v>
       </c>
-      <c r="H50" s="7">
+      <c r="I50" s="7">
         <v>447.33</v>
       </c>
-      <c r="I50">
+      <c r="J50" s="5">
         <v>0.30000000000000004</v>
       </c>
-      <c r="J50">
+      <c r="K50" s="5">
         <v>0</v>
       </c>
-      <c r="K50">
+      <c r="L50" s="5">
         <v>0.30000000000000004</v>
       </c>
-      <c r="L50">
+      <c r="M50" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N50" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O50" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P50" s="5">
         <v>46.5</v>
       </c>
-      <c r="M50" s="6">
+      <c r="Q50" s="6">
         <v>662</v>
       </c>
-      <c r="N50">
+      <c r="R50" s="5">
         <v>19.087499999999999</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A51" s="6" t="s">
-        <v>26</v>
+        <v>71</v>
       </c>
       <c r="B51" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C51" s="6">
         <v>2024</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E51" s="6">
+        <v>12</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F51" s="6">
         <v>2</v>
       </c>
-      <c r="F51" s="6">
+      <c r="G51" s="6">
         <v>205</v>
       </c>
-      <c r="G51">
+      <c r="H51" s="5">
         <v>45</v>
       </c>
-      <c r="H51" s="7">
+      <c r="I51" s="7">
         <v>450.995</v>
       </c>
-      <c r="I51">
+      <c r="J51" s="5">
         <v>1.125</v>
       </c>
-      <c r="J51">
+      <c r="K51" s="5">
         <v>17.740000000000002</v>
       </c>
-      <c r="K51">
+      <c r="L51" s="5">
         <v>18.865000000000002</v>
       </c>
-      <c r="L51">
+      <c r="M51" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N51" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O51" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P51" s="5">
         <v>39.5</v>
       </c>
-      <c r="M51" s="6">
+      <c r="Q51" s="6">
         <v>530</v>
       </c>
-      <c r="N51">
+      <c r="R51" s="5">
         <v>18.11</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A52" s="6" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C52" s="6">
         <v>2024</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E52" s="6">
+        <v>12</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F52" s="6">
         <v>3</v>
       </c>
-      <c r="F52" s="6">
+      <c r="G52" s="6">
         <v>301</v>
       </c>
-      <c r="G52">
+      <c r="H52" s="5">
         <v>46.5</v>
       </c>
-      <c r="H52" s="7">
+      <c r="I52" s="7">
         <v>464</v>
       </c>
-      <c r="I52">
+      <c r="J52" s="5">
         <v>0.20499999999999999</v>
       </c>
-      <c r="J52">
+      <c r="K52" s="5">
         <v>0</v>
       </c>
-      <c r="K52">
+      <c r="L52" s="5">
         <v>0.20499999999999999</v>
       </c>
-      <c r="L52">
+      <c r="M52" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N52" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O52" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P52" s="5">
         <v>42</v>
       </c>
-      <c r="M52" s="6">
+      <c r="Q52" s="6">
         <v>642</v>
       </c>
-      <c r="N52">
+      <c r="R52" s="5">
         <v>18.6175</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A53" s="6" t="s">
-        <v>28</v>
+        <v>73</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C53" s="6">
         <v>2024</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="6">
+        <v>13</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F53" s="6">
         <v>3</v>
       </c>
-      <c r="F53" s="6">
+      <c r="G53" s="6">
         <v>302</v>
       </c>
-      <c r="G53">
+      <c r="H53" s="5">
         <v>46.5</v>
       </c>
-      <c r="H53" s="7">
+      <c r="I53" s="7">
         <v>445.995</v>
       </c>
-      <c r="I53">
+      <c r="J53" s="5">
         <v>11.75</v>
       </c>
-      <c r="J53">
+      <c r="K53" s="5">
         <v>5.87</v>
       </c>
-      <c r="K53">
+      <c r="L53" s="5">
         <v>17.62</v>
       </c>
-      <c r="L53">
+      <c r="M53" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N53" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O53" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P53" s="5">
         <v>37.5</v>
       </c>
-      <c r="M53" s="6">
+      <c r="Q53" s="6">
         <v>498</v>
       </c>
-      <c r="N53">
+      <c r="R53" s="5">
         <v>17.655000000000001</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A54" s="6" t="s">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C54" s="6">
         <v>2024</v>
       </c>
       <c r="D54" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F54" s="6">
+        <v>3</v>
+      </c>
+      <c r="G54" s="6">
+        <v>303</v>
+      </c>
+      <c r="H54" s="5">
+        <v>43</v>
+      </c>
+      <c r="I54" s="7">
+        <v>469.65499999999997</v>
+      </c>
+      <c r="J54" s="5">
+        <v>0.11000000000000001</v>
+      </c>
+      <c r="K54" s="5">
+        <v>0.05</v>
+      </c>
+      <c r="L54" s="5">
+        <v>0.16000000000000003</v>
+      </c>
+      <c r="M54">
+        <v>47.11</v>
+      </c>
+      <c r="N54">
+        <v>181.315</v>
+      </c>
+      <c r="O54">
+        <v>228.42500000000001</v>
+      </c>
+      <c r="P54" s="5">
+        <v>47</v>
+      </c>
+      <c r="Q54" s="6">
+        <v>688</v>
+      </c>
+      <c r="R54" s="5">
+        <v>17.8125</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A55" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="E54" s="6">
-        <v>3</v>
-      </c>
-      <c r="F54" s="6">
-        <v>303</v>
-      </c>
-      <c r="G54">
-        <v>43</v>
-      </c>
-      <c r="H54" s="7">
-        <v>469.65499999999997</v>
-      </c>
-      <c r="I54">
-        <v>0.11000000000000001</v>
-      </c>
-      <c r="J54">
-        <v>0.05</v>
-      </c>
-      <c r="K54">
-        <v>0.16000000000000003</v>
-      </c>
-      <c r="L54">
-        <v>47</v>
-      </c>
-      <c r="M54" s="6">
-        <v>688</v>
-      </c>
-      <c r="N54">
-        <v>17.8125</v>
-      </c>
-    </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C55" s="6">
         <v>2024</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E55" s="6">
+        <v>14</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F55" s="6">
         <v>3</v>
       </c>
-      <c r="F55" s="6">
+      <c r="G55" s="6">
         <v>304</v>
       </c>
-      <c r="G55">
+      <c r="H55" s="5">
         <v>50</v>
       </c>
-      <c r="H55" s="7">
+      <c r="I55" s="7">
         <v>416.95</v>
       </c>
-      <c r="I55">
+      <c r="J55" s="5">
         <v>0</v>
       </c>
-      <c r="J55">
+      <c r="K55" s="5">
         <v>0.73</v>
       </c>
-      <c r="K55">
+      <c r="L55" s="5">
         <v>0.73</v>
       </c>
-      <c r="L55">
+      <c r="M55">
+        <v>61.564999999999998</v>
+      </c>
+      <c r="N55">
+        <v>186.03</v>
+      </c>
+      <c r="O55">
+        <v>247.59500000000003</v>
+      </c>
+      <c r="P55" s="5">
         <v>54</v>
       </c>
-      <c r="M55" s="6">
+      <c r="Q55" s="6">
         <v>712</v>
       </c>
-      <c r="N55">
+      <c r="R55" s="5">
         <v>17.872499999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A56" s="6" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C56" s="6">
         <v>2024</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E56" s="6">
+        <v>15</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F56" s="6">
         <v>3</v>
       </c>
-      <c r="F56" s="6">
+      <c r="G56" s="6">
         <v>305</v>
       </c>
-      <c r="G56">
+      <c r="H56" s="5">
         <v>44.5</v>
       </c>
-      <c r="H56" s="7">
+      <c r="I56" s="7">
         <v>472.68</v>
       </c>
-      <c r="I56">
+      <c r="J56" s="5">
         <v>0</v>
       </c>
-      <c r="J56">
+      <c r="K56" s="5">
         <v>23</v>
       </c>
-      <c r="K56">
+      <c r="L56" s="5">
         <v>23</v>
       </c>
-      <c r="L56">
+      <c r="M56">
+        <v>91.134999999999991</v>
+      </c>
+      <c r="N56">
+        <v>254.36</v>
+      </c>
+      <c r="O56">
+        <v>345.495</v>
+      </c>
+      <c r="P56" s="5">
         <v>45.5</v>
       </c>
-      <c r="M56" s="6">
+      <c r="Q56" s="6">
         <v>666</v>
       </c>
-      <c r="N56">
+      <c r="R56" s="5">
         <v>17.732499999999998</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A57" s="6" t="s">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C57" s="6">
         <v>2024</v>
       </c>
       <c r="D57" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F57" s="6">
+        <v>4</v>
+      </c>
+      <c r="G57" s="6">
+        <v>401</v>
+      </c>
+      <c r="H57" s="5">
+        <v>41</v>
+      </c>
+      <c r="I57" s="7">
+        <v>437.55</v>
+      </c>
+      <c r="J57" s="5">
+        <v>0</v>
+      </c>
+      <c r="K57" s="5">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="L57" s="5">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="M57">
+        <v>65.364999999999995</v>
+      </c>
+      <c r="N57">
+        <v>241.92000000000002</v>
+      </c>
+      <c r="O57">
+        <v>307.28499999999997</v>
+      </c>
+      <c r="P57" s="5">
+        <v>53</v>
+      </c>
+      <c r="Q57" s="6">
+        <v>730</v>
+      </c>
+      <c r="R57" s="5">
+        <v>18.12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" ht="17" x14ac:dyDescent="0.2">
+      <c r="A58" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B58" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="E57" s="6">
-        <v>4</v>
-      </c>
-      <c r="F57" s="6">
-        <v>401</v>
-      </c>
-      <c r="G57">
-        <v>41</v>
-      </c>
-      <c r="H57" s="7">
-        <v>437.55</v>
-      </c>
-      <c r="I57">
-        <v>0</v>
-      </c>
-      <c r="J57">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="K57">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="L57">
-        <v>53</v>
-      </c>
-      <c r="M57" s="6">
-        <v>730</v>
-      </c>
-      <c r="N57">
-        <v>18.12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B58" s="6" t="s">
-        <v>38</v>
       </c>
       <c r="C58" s="6">
         <v>2024</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="E58" s="6">
+        <v>15</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F58" s="6">
         <v>4</v>
       </c>
-      <c r="F58" s="6">
+      <c r="G58" s="6">
         <v>402</v>
       </c>
-      <c r="G58">
+      <c r="H58" s="5">
         <v>37.5</v>
       </c>
-      <c r="H58" s="7">
+      <c r="I58" s="7">
         <v>396.495</v>
       </c>
-      <c r="I58">
+      <c r="J58" s="5">
         <v>0</v>
       </c>
-      <c r="J58">
+      <c r="K58" s="5">
         <v>1.95</v>
       </c>
-      <c r="K58">
+      <c r="L58" s="5">
         <v>1.95</v>
       </c>
-      <c r="L58">
+      <c r="M58">
+        <v>82.56</v>
+      </c>
+      <c r="N58">
+        <v>233.4</v>
+      </c>
+      <c r="O58">
+        <v>315.96000000000004</v>
+      </c>
+      <c r="P58" s="5">
         <v>40.5</v>
       </c>
-      <c r="M58" s="6">
+      <c r="Q58" s="6">
         <v>688</v>
       </c>
-      <c r="N58">
+      <c r="R58" s="5">
         <v>17.652499999999996</v>
       </c>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A59" s="6" t="s">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C59" s="6">
         <v>2024</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E59" s="6">
+        <v>14</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F59" s="6">
         <v>4</v>
       </c>
-      <c r="F59" s="6">
+      <c r="G59" s="6">
         <v>403</v>
       </c>
-      <c r="G59">
+      <c r="H59" s="5">
         <v>42.5</v>
       </c>
-      <c r="H59" s="7">
+      <c r="I59" s="7">
         <v>378.375</v>
       </c>
-      <c r="I59">
+      <c r="J59" s="5">
         <v>0</v>
       </c>
-      <c r="J59">
+      <c r="K59" s="5">
         <v>3.36</v>
       </c>
-      <c r="K59">
+      <c r="L59" s="5">
         <v>3.36</v>
       </c>
-      <c r="L59">
+      <c r="M59">
+        <v>68.510000000000005</v>
+      </c>
+      <c r="N59">
+        <v>288.625</v>
+      </c>
+      <c r="O59">
+        <v>357.13499999999999</v>
+      </c>
+      <c r="P59" s="5">
         <v>44.5</v>
       </c>
-      <c r="M59" s="6">
+      <c r="Q59" s="6">
         <v>614</v>
       </c>
-      <c r="N59">
+      <c r="R59" s="5">
         <v>17.892500000000002</v>
       </c>
     </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A60" s="6" t="s">
-        <v>35</v>
+        <v>80</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C60" s="6">
         <v>2024</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E60" s="6">
+        <v>13</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F60" s="6">
         <v>4</v>
       </c>
-      <c r="F60" s="6">
+      <c r="G60" s="6">
         <v>404</v>
       </c>
-      <c r="G60">
+      <c r="H60" s="5">
         <v>47.5</v>
       </c>
-      <c r="H60" s="7">
+      <c r="I60" s="7">
         <v>434.96</v>
       </c>
-      <c r="I60">
+      <c r="J60" s="5">
         <v>0</v>
       </c>
-      <c r="J60">
+      <c r="K60" s="5">
         <v>0.20499999999999999</v>
       </c>
-      <c r="K60">
+      <c r="L60" s="5">
         <v>0.20499999999999999</v>
       </c>
-      <c r="L60">
+      <c r="M60" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N60" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O60" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P60" s="5">
         <v>45</v>
       </c>
-      <c r="M60" s="6">
+      <c r="Q60" s="6">
         <v>678</v>
       </c>
-      <c r="N60">
+      <c r="R60" s="5">
         <v>18.8125</v>
       </c>
     </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:18" ht="17" x14ac:dyDescent="0.2">
       <c r="A61" s="6" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="C61" s="6">
         <v>2024</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E61" s="6">
+        <v>12</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="F61" s="6">
         <v>4</v>
       </c>
-      <c r="F61" s="6">
+      <c r="G61" s="6">
         <v>405</v>
       </c>
-      <c r="G61">
+      <c r="H61" s="5">
         <v>36.5</v>
       </c>
-      <c r="H61" s="7">
+      <c r="I61" s="7">
         <v>426.1</v>
       </c>
-      <c r="I61">
+      <c r="J61" s="5">
         <v>1.335</v>
       </c>
-      <c r="J61">
+      <c r="K61" s="5">
         <v>3.6999999999999997</v>
       </c>
-      <c r="K61">
+      <c r="L61" s="5">
         <v>5.0350000000000001</v>
       </c>
-      <c r="L61">
+      <c r="M61" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="N61" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="O61" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="P61" s="5">
         <v>45.5</v>
       </c>
-      <c r="M61" s="6">
+      <c r="Q61" s="6">
         <v>656</v>
       </c>
-      <c r="N61">
+      <c r="R61" s="5">
         <v>19.4925</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/raw/All Treatments/combined_raw.xlsx
+++ b/data/raw/All Treatments/combined_raw.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ey239/Github/Mowtivation/data/raw/All Treatments/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1757DF03-7787-8C40-BEE2-545578492D69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCD09C7A-7F1A-7546-B0E9-0DEF4D10F943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3680" yWindow="-20800" windowWidth="19220" windowHeight="21000" xr2:uid="{BC6E1F37-F489-F945-938B-9CB0E83CEE7D}"/>
+    <workbookView xWindow="12840" yWindow="980" windowWidth="17280" windowHeight="20480" xr2:uid="{BC6E1F37-F489-F945-938B-9CB0E83CEE7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -302,10 +302,10 @@
     <t>cereal_rye_variety</t>
   </si>
   <si>
-    <t>aroostook</t>
-  </si>
-  <si>
-    <t>nd gardner</t>
+    <t>Aroostook</t>
+  </si>
+  <si>
+    <t>Nd Gardner</t>
   </si>
 </sst>
 </file>
@@ -745,9 +745,9 @@
     <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.1640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.83203125" customWidth="1"/>
     <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="20.83203125" bestFit="1" customWidth="1"/>
@@ -770,16 +770,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>6</v>
@@ -825,17 +825,17 @@
       <c r="C2" s="6">
         <v>2023</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="6">
+        <v>1</v>
+      </c>
+      <c r="E2" s="6">
+        <v>101</v>
+      </c>
+      <c r="F2" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F2" s="6">
-        <v>1</v>
-      </c>
-      <c r="G2" s="6">
-        <v>101</v>
       </c>
       <c r="H2" s="5">
         <v>46.5</v>
@@ -881,17 +881,17 @@
       <c r="C3" s="6">
         <v>2023</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="6">
+        <v>1</v>
+      </c>
+      <c r="E3" s="6">
+        <v>102</v>
+      </c>
+      <c r="F3" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F3" s="6">
-        <v>1</v>
-      </c>
-      <c r="G3" s="6">
-        <v>102</v>
       </c>
       <c r="H3" s="5">
         <v>42.5</v>
@@ -937,17 +937,17 @@
       <c r="C4" s="6">
         <v>2023</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="6">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6">
+        <v>103</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F4" s="6">
-        <v>1</v>
-      </c>
-      <c r="G4" s="6">
-        <v>103</v>
       </c>
       <c r="H4" s="5">
         <v>36.5</v>
@@ -993,17 +993,17 @@
       <c r="C5" s="6">
         <v>2023</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="6">
+        <v>1</v>
+      </c>
+      <c r="E5" s="6">
+        <v>104</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F5" s="6">
-        <v>1</v>
-      </c>
-      <c r="G5" s="6">
-        <v>104</v>
       </c>
       <c r="H5" s="5">
         <v>41</v>
@@ -1049,17 +1049,17 @@
       <c r="C6" s="6">
         <v>2023</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="6">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6">
+        <v>105</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F6" s="6">
-        <v>1</v>
-      </c>
-      <c r="G6" s="6">
-        <v>105</v>
       </c>
       <c r="H6" s="5">
         <v>41</v>
@@ -1105,17 +1105,17 @@
       <c r="C7" s="6">
         <v>2023</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="6">
+        <v>2</v>
+      </c>
+      <c r="E7" s="6">
+        <v>201</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F7" s="6">
-        <v>2</v>
-      </c>
-      <c r="G7" s="6">
-        <v>201</v>
       </c>
       <c r="H7" s="5">
         <v>36.5</v>
@@ -1161,17 +1161,17 @@
       <c r="C8" s="6">
         <v>2023</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>202</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F8" s="6">
-        <v>2</v>
-      </c>
-      <c r="G8" s="6">
-        <v>202</v>
       </c>
       <c r="H8" s="5">
         <v>39</v>
@@ -1217,17 +1217,17 @@
       <c r="C9" s="6">
         <v>2023</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="6">
+        <v>2</v>
+      </c>
+      <c r="E9" s="6">
+        <v>203</v>
+      </c>
+      <c r="F9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="G9" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F9" s="6">
-        <v>2</v>
-      </c>
-      <c r="G9" s="6">
-        <v>203</v>
       </c>
       <c r="H9" s="5">
         <v>40</v>
@@ -1273,17 +1273,17 @@
       <c r="C10" s="6">
         <v>2023</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="6">
+        <v>2</v>
+      </c>
+      <c r="E10" s="6">
+        <v>204</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="G10" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F10" s="6">
-        <v>2</v>
-      </c>
-      <c r="G10" s="6">
-        <v>204</v>
       </c>
       <c r="H10" s="5">
         <v>45.5</v>
@@ -1329,17 +1329,17 @@
       <c r="C11" s="6">
         <v>2023</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6">
+        <v>205</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F11" s="6">
-        <v>2</v>
-      </c>
-      <c r="G11" s="6">
-        <v>205</v>
       </c>
       <c r="H11" s="5">
         <v>44.5</v>
@@ -1385,17 +1385,17 @@
       <c r="C12" s="6">
         <v>2023</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="6">
+        <v>3</v>
+      </c>
+      <c r="E12" s="6">
+        <v>301</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F12" s="6">
-        <v>3</v>
-      </c>
-      <c r="G12" s="6">
-        <v>301</v>
       </c>
       <c r="H12" s="5">
         <v>46</v>
@@ -1441,17 +1441,17 @@
       <c r="C13" s="6">
         <v>2023</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="6">
+        <v>3</v>
+      </c>
+      <c r="E13" s="6">
+        <v>302</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F13" s="6">
-        <v>3</v>
-      </c>
-      <c r="G13" s="6">
-        <v>302</v>
       </c>
       <c r="H13" s="5">
         <v>41</v>
@@ -1497,17 +1497,17 @@
       <c r="C14" s="6">
         <v>2023</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="6">
+        <v>3</v>
+      </c>
+      <c r="E14" s="6">
+        <v>303</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F14" s="6">
-        <v>3</v>
-      </c>
-      <c r="G14" s="6">
-        <v>303</v>
       </c>
       <c r="H14" s="5">
         <v>36.5</v>
@@ -1553,17 +1553,17 @@
       <c r="C15" s="6">
         <v>2023</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="6">
+        <v>3</v>
+      </c>
+      <c r="E15" s="6">
+        <v>304</v>
+      </c>
+      <c r="F15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F15" s="6">
-        <v>3</v>
-      </c>
-      <c r="G15" s="6">
-        <v>304</v>
       </c>
       <c r="H15" s="5">
         <v>39.5</v>
@@ -1609,17 +1609,17 @@
       <c r="C16" s="6">
         <v>2023</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="6">
+        <v>3</v>
+      </c>
+      <c r="E16" s="6">
+        <v>305</v>
+      </c>
+      <c r="F16" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F16" s="6">
-        <v>3</v>
-      </c>
-      <c r="G16" s="6">
-        <v>305</v>
       </c>
       <c r="H16" s="5">
         <v>38.5</v>
@@ -1665,17 +1665,17 @@
       <c r="C17" s="6">
         <v>2023</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="6">
+        <v>4</v>
+      </c>
+      <c r="E17" s="6">
+        <v>401</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F17" s="6">
-        <v>4</v>
-      </c>
-      <c r="G17" s="6">
-        <v>401</v>
       </c>
       <c r="H17" s="5">
         <v>43.5</v>
@@ -1721,17 +1721,17 @@
       <c r="C18" s="6">
         <v>2023</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="6">
+        <v>4</v>
+      </c>
+      <c r="E18" s="6">
+        <v>402</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="G18" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F18" s="6">
-        <v>4</v>
-      </c>
-      <c r="G18" s="6">
-        <v>402</v>
       </c>
       <c r="H18" s="5">
         <v>36</v>
@@ -1777,17 +1777,17 @@
       <c r="C19" s="6">
         <v>2023</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="6">
+        <v>4</v>
+      </c>
+      <c r="E19" s="6">
+        <v>403</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="G19" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F19" s="6">
-        <v>4</v>
-      </c>
-      <c r="G19" s="6">
-        <v>403</v>
       </c>
       <c r="H19" s="5">
         <v>36</v>
@@ -1833,17 +1833,17 @@
       <c r="C20" s="6">
         <v>2023</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="6">
+        <v>4</v>
+      </c>
+      <c r="E20" s="6">
+        <v>404</v>
+      </c>
+      <c r="F20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E20" s="6" t="s">
+      <c r="G20" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F20" s="6">
-        <v>4</v>
-      </c>
-      <c r="G20" s="6">
-        <v>404</v>
       </c>
       <c r="H20" s="5">
         <v>45.5</v>
@@ -1889,17 +1889,17 @@
       <c r="C21" s="6">
         <v>2023</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="6">
+        <v>4</v>
+      </c>
+      <c r="E21" s="6">
+        <v>405</v>
+      </c>
+      <c r="F21" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="6" t="s">
+      <c r="G21" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F21" s="6">
-        <v>4</v>
-      </c>
-      <c r="G21" s="6">
-        <v>405</v>
       </c>
       <c r="H21" s="5">
         <v>43</v>
@@ -1945,17 +1945,17 @@
       <c r="C22" s="6">
         <v>2024</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="6">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6">
+        <v>101</v>
+      </c>
+      <c r="F22" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="G22" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F22" s="6">
-        <v>1</v>
-      </c>
-      <c r="G22" s="6">
-        <v>101</v>
       </c>
       <c r="H22" s="5">
         <v>47.5</v>
@@ -2001,17 +2001,17 @@
       <c r="C23" s="6">
         <v>2024</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="6">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6">
+        <v>102</v>
+      </c>
+      <c r="F23" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F23" s="6">
-        <v>1</v>
-      </c>
-      <c r="G23" s="6">
-        <v>102</v>
       </c>
       <c r="H23" s="5">
         <v>47.5</v>
@@ -2057,17 +2057,17 @@
       <c r="C24" s="6">
         <v>2024</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="6">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6">
+        <v>103</v>
+      </c>
+      <c r="F24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="G24" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F24" s="6">
-        <v>1</v>
-      </c>
-      <c r="G24" s="6">
-        <v>103</v>
       </c>
       <c r="H24" s="5">
         <v>44.5</v>
@@ -2113,17 +2113,17 @@
       <c r="C25" s="6">
         <v>2024</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="6">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6">
+        <v>104</v>
+      </c>
+      <c r="F25" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="G25" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F25" s="6">
-        <v>1</v>
-      </c>
-      <c r="G25" s="6">
-        <v>104</v>
       </c>
       <c r="H25" s="5">
         <v>40</v>
@@ -2169,17 +2169,17 @@
       <c r="C26" s="6">
         <v>2024</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="6">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6">
+        <v>105</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="G26" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F26" s="6">
-        <v>1</v>
-      </c>
-      <c r="G26" s="6">
-        <v>105</v>
       </c>
       <c r="H26" s="5">
         <v>40</v>
@@ -2225,17 +2225,17 @@
       <c r="C27" s="6">
         <v>2024</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="6">
+        <v>2</v>
+      </c>
+      <c r="E27" s="6">
+        <v>201</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="G27" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F27" s="6">
-        <v>2</v>
-      </c>
-      <c r="G27" s="6">
-        <v>201</v>
       </c>
       <c r="H27" s="5">
         <v>47.5</v>
@@ -2281,17 +2281,17 @@
       <c r="C28" s="6">
         <v>2024</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="6">
+        <v>2</v>
+      </c>
+      <c r="E28" s="6">
+        <v>202</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="6" t="s">
+      <c r="G28" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F28" s="6">
-        <v>2</v>
-      </c>
-      <c r="G28" s="6">
-        <v>202</v>
       </c>
       <c r="H28" s="5">
         <v>43</v>
@@ -2337,17 +2337,17 @@
       <c r="C29" s="6">
         <v>2024</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="6">
+        <v>2</v>
+      </c>
+      <c r="E29" s="6">
+        <v>203</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="6" t="s">
+      <c r="G29" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F29" s="6">
-        <v>2</v>
-      </c>
-      <c r="G29" s="6">
-        <v>203</v>
       </c>
       <c r="H29" s="5">
         <v>41.5</v>
@@ -2393,17 +2393,17 @@
       <c r="C30" s="6">
         <v>2024</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="6">
+        <v>2</v>
+      </c>
+      <c r="E30" s="6">
+        <v>204</v>
+      </c>
+      <c r="F30" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="G30" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F30" s="6">
-        <v>2</v>
-      </c>
-      <c r="G30" s="6">
-        <v>204</v>
       </c>
       <c r="H30" s="5">
         <v>47</v>
@@ -2449,17 +2449,17 @@
       <c r="C31" s="6">
         <v>2024</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="6">
+        <v>2</v>
+      </c>
+      <c r="E31" s="6">
+        <v>205</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="G31" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F31" s="6">
-        <v>2</v>
-      </c>
-      <c r="G31" s="6">
-        <v>205</v>
       </c>
       <c r="H31" s="5">
         <v>46</v>
@@ -2505,17 +2505,17 @@
       <c r="C32" s="6">
         <v>2024</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="6">
+        <v>3</v>
+      </c>
+      <c r="E32" s="6">
+        <v>301</v>
+      </c>
+      <c r="F32" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="6" t="s">
+      <c r="G32" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F32" s="6">
-        <v>3</v>
-      </c>
-      <c r="G32" s="6">
-        <v>301</v>
       </c>
       <c r="H32" s="5">
         <v>47.5</v>
@@ -2561,17 +2561,17 @@
       <c r="C33" s="6">
         <v>2024</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="6">
+        <v>3</v>
+      </c>
+      <c r="E33" s="6">
+        <v>302</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E33" s="6" t="s">
+      <c r="G33" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F33" s="6">
-        <v>3</v>
-      </c>
-      <c r="G33" s="6">
-        <v>302</v>
       </c>
       <c r="H33" s="5">
         <v>41.5</v>
@@ -2617,17 +2617,17 @@
       <c r="C34" s="6">
         <v>2024</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="6">
+        <v>3</v>
+      </c>
+      <c r="E34" s="6">
+        <v>303</v>
+      </c>
+      <c r="F34" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="G34" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F34" s="6">
-        <v>3</v>
-      </c>
-      <c r="G34" s="6">
-        <v>303</v>
       </c>
       <c r="H34" s="5">
         <v>53.5</v>
@@ -2673,17 +2673,17 @@
       <c r="C35" s="6">
         <v>2024</v>
       </c>
-      <c r="D35" s="6" t="s">
+      <c r="D35" s="6">
+        <v>3</v>
+      </c>
+      <c r="E35" s="6">
+        <v>304</v>
+      </c>
+      <c r="F35" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E35" s="6" t="s">
+      <c r="G35" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F35" s="6">
-        <v>3</v>
-      </c>
-      <c r="G35" s="6">
-        <v>304</v>
       </c>
       <c r="H35" s="5">
         <v>54</v>
@@ -2729,17 +2729,17 @@
       <c r="C36" s="6">
         <v>2024</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="6">
+        <v>3</v>
+      </c>
+      <c r="E36" s="6">
+        <v>305</v>
+      </c>
+      <c r="F36" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="G36" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F36" s="6">
-        <v>3</v>
-      </c>
-      <c r="G36" s="6">
-        <v>305</v>
       </c>
       <c r="H36" s="5">
         <v>42.5</v>
@@ -2785,17 +2785,17 @@
       <c r="C37" s="6">
         <v>2024</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="6">
+        <v>4</v>
+      </c>
+      <c r="E37" s="6">
+        <v>401</v>
+      </c>
+      <c r="F37" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E37" s="6" t="s">
+      <c r="G37" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F37" s="6">
-        <v>4</v>
-      </c>
-      <c r="G37" s="6">
-        <v>401</v>
       </c>
       <c r="H37" s="5">
         <v>42</v>
@@ -2841,17 +2841,17 @@
       <c r="C38" s="6">
         <v>2024</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="6">
+        <v>4</v>
+      </c>
+      <c r="E38" s="6">
+        <v>402</v>
+      </c>
+      <c r="F38" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E38" s="6" t="s">
+      <c r="G38" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F38" s="6">
-        <v>4</v>
-      </c>
-      <c r="G38" s="6">
-        <v>402</v>
       </c>
       <c r="H38" s="5">
         <v>43.5</v>
@@ -2897,17 +2897,17 @@
       <c r="C39" s="6">
         <v>2024</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="6">
+        <v>4</v>
+      </c>
+      <c r="E39" s="6">
+        <v>403</v>
+      </c>
+      <c r="F39" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="G39" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F39" s="6">
-        <v>4</v>
-      </c>
-      <c r="G39" s="6">
-        <v>403</v>
       </c>
       <c r="H39" s="5">
         <v>44.5</v>
@@ -2953,17 +2953,17 @@
       <c r="C40" s="6">
         <v>2024</v>
       </c>
-      <c r="D40" s="6" t="s">
+      <c r="D40" s="6">
+        <v>4</v>
+      </c>
+      <c r="E40" s="6">
+        <v>404</v>
+      </c>
+      <c r="F40" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E40" s="6" t="s">
+      <c r="G40" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F40" s="6">
-        <v>4</v>
-      </c>
-      <c r="G40" s="6">
-        <v>404</v>
       </c>
       <c r="H40" s="5">
         <v>45</v>
@@ -3009,17 +3009,17 @@
       <c r="C41" s="6">
         <v>2024</v>
       </c>
-      <c r="D41" s="6" t="s">
+      <c r="D41" s="6">
+        <v>4</v>
+      </c>
+      <c r="E41" s="6">
+        <v>405</v>
+      </c>
+      <c r="F41" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E41" s="6" t="s">
+      <c r="G41" s="6" t="s">
         <v>87</v>
-      </c>
-      <c r="F41" s="6">
-        <v>4</v>
-      </c>
-      <c r="G41" s="6">
-        <v>405</v>
       </c>
       <c r="H41" s="5">
         <v>50</v>
@@ -3065,17 +3065,17 @@
       <c r="C42" s="6">
         <v>2024</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="6">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6">
+        <v>101</v>
+      </c>
+      <c r="F42" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="G42" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F42" s="6">
-        <v>1</v>
-      </c>
-      <c r="G42" s="6">
-        <v>101</v>
       </c>
       <c r="H42" s="5">
         <v>51.5</v>
@@ -3121,17 +3121,17 @@
       <c r="C43" s="6">
         <v>2024</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="6">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6">
+        <v>102</v>
+      </c>
+      <c r="F43" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="6" t="s">
+      <c r="G43" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F43" s="6">
-        <v>1</v>
-      </c>
-      <c r="G43" s="6">
-        <v>102</v>
       </c>
       <c r="H43" s="5">
         <v>49.5</v>
@@ -3177,17 +3177,17 @@
       <c r="C44" s="6">
         <v>2024</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="6">
+        <v>1</v>
+      </c>
+      <c r="E44" s="6">
+        <v>103</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E44" s="6" t="s">
+      <c r="G44" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F44" s="6">
-        <v>1</v>
-      </c>
-      <c r="G44" s="6">
-        <v>103</v>
       </c>
       <c r="H44" s="5">
         <v>43</v>
@@ -3233,17 +3233,17 @@
       <c r="C45" s="6">
         <v>2024</v>
       </c>
-      <c r="D45" s="6" t="s">
+      <c r="D45" s="6">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6">
+        <v>104</v>
+      </c>
+      <c r="F45" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E45" s="6" t="s">
+      <c r="G45" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F45" s="6">
-        <v>1</v>
-      </c>
-      <c r="G45" s="6">
-        <v>104</v>
       </c>
       <c r="H45" s="5">
         <v>45.5</v>
@@ -3289,17 +3289,17 @@
       <c r="C46" s="6">
         <v>2024</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="6">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6">
+        <v>105</v>
+      </c>
+      <c r="F46" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="G46" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F46" s="6">
-        <v>1</v>
-      </c>
-      <c r="G46" s="6">
-        <v>105</v>
       </c>
       <c r="H46" s="5">
         <v>38.5</v>
@@ -3345,17 +3345,17 @@
       <c r="C47" s="6">
         <v>2024</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="6">
+        <v>2</v>
+      </c>
+      <c r="E47" s="6">
+        <v>201</v>
+      </c>
+      <c r="F47" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E47" s="6" t="s">
+      <c r="G47" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F47" s="6">
-        <v>2</v>
-      </c>
-      <c r="G47" s="6">
-        <v>201</v>
       </c>
       <c r="H47" s="5">
         <v>46.5</v>
@@ -3401,17 +3401,17 @@
       <c r="C48" s="6">
         <v>2024</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="6">
+        <v>2</v>
+      </c>
+      <c r="E48" s="6">
+        <v>202</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="6" t="s">
+      <c r="G48" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F48" s="6">
-        <v>2</v>
-      </c>
-      <c r="G48" s="6">
-        <v>202</v>
       </c>
       <c r="H48" s="5">
         <v>43.5</v>
@@ -3457,17 +3457,17 @@
       <c r="C49" s="6">
         <v>2024</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D49" s="6">
+        <v>2</v>
+      </c>
+      <c r="E49" s="6">
+        <v>203</v>
+      </c>
+      <c r="F49" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E49" s="6" t="s">
+      <c r="G49" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F49" s="6">
-        <v>2</v>
-      </c>
-      <c r="G49" s="6">
-        <v>203</v>
       </c>
       <c r="H49" s="5">
         <v>43</v>
@@ -3513,17 +3513,17 @@
       <c r="C50" s="6">
         <v>2024</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="6">
+        <v>2</v>
+      </c>
+      <c r="E50" s="6">
+        <v>204</v>
+      </c>
+      <c r="F50" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="G50" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F50" s="6">
-        <v>2</v>
-      </c>
-      <c r="G50" s="6">
-        <v>204</v>
       </c>
       <c r="H50" s="5">
         <v>51.5</v>
@@ -3569,17 +3569,17 @@
       <c r="C51" s="6">
         <v>2024</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="6">
+        <v>2</v>
+      </c>
+      <c r="E51" s="6">
+        <v>205</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="G51" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F51" s="6">
-        <v>2</v>
-      </c>
-      <c r="G51" s="6">
-        <v>205</v>
       </c>
       <c r="H51" s="5">
         <v>45</v>
@@ -3625,17 +3625,17 @@
       <c r="C52" s="6">
         <v>2024</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="6">
+        <v>3</v>
+      </c>
+      <c r="E52" s="6">
+        <v>301</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="G52" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F52" s="6">
-        <v>3</v>
-      </c>
-      <c r="G52" s="6">
-        <v>301</v>
       </c>
       <c r="H52" s="5">
         <v>46.5</v>
@@ -3681,17 +3681,17 @@
       <c r="C53" s="6">
         <v>2024</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D53" s="6">
+        <v>3</v>
+      </c>
+      <c r="E53" s="6">
+        <v>302</v>
+      </c>
+      <c r="F53" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="G53" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F53" s="6">
-        <v>3</v>
-      </c>
-      <c r="G53" s="6">
-        <v>302</v>
       </c>
       <c r="H53" s="5">
         <v>46.5</v>
@@ -3737,17 +3737,17 @@
       <c r="C54" s="6">
         <v>2024</v>
       </c>
-      <c r="D54" s="6" t="s">
+      <c r="D54" s="6">
+        <v>3</v>
+      </c>
+      <c r="E54" s="6">
+        <v>303</v>
+      </c>
+      <c r="F54" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="G54" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F54" s="6">
-        <v>3</v>
-      </c>
-      <c r="G54" s="6">
-        <v>303</v>
       </c>
       <c r="H54" s="5">
         <v>43</v>
@@ -3793,17 +3793,17 @@
       <c r="C55" s="6">
         <v>2024</v>
       </c>
-      <c r="D55" s="6" t="s">
+      <c r="D55" s="6">
+        <v>3</v>
+      </c>
+      <c r="E55" s="6">
+        <v>304</v>
+      </c>
+      <c r="F55" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="G55" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F55" s="6">
-        <v>3</v>
-      </c>
-      <c r="G55" s="6">
-        <v>304</v>
       </c>
       <c r="H55" s="5">
         <v>50</v>
@@ -3849,17 +3849,17 @@
       <c r="C56" s="6">
         <v>2024</v>
       </c>
-      <c r="D56" s="6" t="s">
+      <c r="D56" s="6">
+        <v>3</v>
+      </c>
+      <c r="E56" s="6">
+        <v>305</v>
+      </c>
+      <c r="F56" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="G56" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F56" s="6">
-        <v>3</v>
-      </c>
-      <c r="G56" s="6">
-        <v>305</v>
       </c>
       <c r="H56" s="5">
         <v>44.5</v>
@@ -3905,17 +3905,17 @@
       <c r="C57" s="6">
         <v>2024</v>
       </c>
-      <c r="D57" s="6" t="s">
+      <c r="D57" s="6">
+        <v>4</v>
+      </c>
+      <c r="E57" s="6">
+        <v>401</v>
+      </c>
+      <c r="F57" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="G57" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F57" s="6">
-        <v>4</v>
-      </c>
-      <c r="G57" s="6">
-        <v>401</v>
       </c>
       <c r="H57" s="5">
         <v>41</v>
@@ -3961,17 +3961,17 @@
       <c r="C58" s="6">
         <v>2024</v>
       </c>
-      <c r="D58" s="6" t="s">
+      <c r="D58" s="6">
+        <v>4</v>
+      </c>
+      <c r="E58" s="6">
+        <v>402</v>
+      </c>
+      <c r="F58" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="G58" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F58" s="6">
-        <v>4</v>
-      </c>
-      <c r="G58" s="6">
-        <v>402</v>
       </c>
       <c r="H58" s="5">
         <v>37.5</v>
@@ -4017,17 +4017,17 @@
       <c r="C59" s="6">
         <v>2024</v>
       </c>
-      <c r="D59" s="6" t="s">
+      <c r="D59" s="6">
+        <v>4</v>
+      </c>
+      <c r="E59" s="6">
+        <v>403</v>
+      </c>
+      <c r="F59" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="G59" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F59" s="6">
-        <v>4</v>
-      </c>
-      <c r="G59" s="6">
-        <v>403</v>
       </c>
       <c r="H59" s="5">
         <v>42.5</v>
@@ -4073,17 +4073,17 @@
       <c r="C60" s="6">
         <v>2024</v>
       </c>
-      <c r="D60" s="6" t="s">
+      <c r="D60" s="6">
+        <v>4</v>
+      </c>
+      <c r="E60" s="6">
+        <v>404</v>
+      </c>
+      <c r="F60" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="G60" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F60" s="6">
-        <v>4</v>
-      </c>
-      <c r="G60" s="6">
-        <v>404</v>
       </c>
       <c r="H60" s="5">
         <v>47.5</v>
@@ -4129,17 +4129,17 @@
       <c r="C61" s="6">
         <v>2024</v>
       </c>
-      <c r="D61" s="6" t="s">
+      <c r="D61" s="6">
+        <v>4</v>
+      </c>
+      <c r="E61" s="6">
+        <v>405</v>
+      </c>
+      <c r="F61" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="G61" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="F61" s="6">
-        <v>4</v>
-      </c>
-      <c r="G61" s="6">
-        <v>405</v>
       </c>
       <c r="H61" s="5">
         <v>36.5</v>
